--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3714-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3714-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E06AFE7A-1F61-4C02-A495-BCFEFE1C35AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43242892-FEAA-45F1-A8AA-4E2904DFDD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{EE14E17B-852F-449B-AC6B-722875B9CF3A}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{69EB0B74-F48E-42AB-AEED-B894BB642CE3}"/>
   </bookViews>
   <sheets>
     <sheet name="3714-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1451,26 +1451,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800BA9EC-855F-4FEC-A8AC-F6912A49DFBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{030BF9B0-F07D-4E84-AD6D-104DEF183351}">
   <dimension ref="A1:X13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="6.75" customWidth="1"/>
-    <col min="5" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="23" width="6.75" customWidth="1"/>
-    <col min="24" max="24" width="9" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="5.88671875" customWidth="1"/>
+    <col min="5" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="23" width="5.88671875" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1504,7 +1504,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1540,7 +1540,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1660,7 +1660,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>32</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>32</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>32</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>32</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>39</v>
       </c>
